--- a/ejes/Políticas/Configuracion_politicas_cultura.xlsx
+++ b/ejes/Políticas/Configuracion_politicas_cultura.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,44 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Instrucción directa de Felipe (2026-05-21): descartar en todos los ejes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PAD Víctimas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Producto transversal a nivel servicio Casas (no se reporta por eje específico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>reincorpor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transversal del servicio Casas, no de un eje. Aparece en Casas servicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PDET</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Transversal del servicio Casas, no de un eje. Aparece en Casas servicio.</t>
         </is>
       </c>
     </row>

--- a/ejes/Políticas/Configuracion_politicas_cultura.xlsx
+++ b/ejes/Políticas/Configuracion_politicas_cultura.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,6 @@
           <t>reincorpor</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Transversal del servicio Casas, no de un eje. Aparece en Casas servicio.</t>
@@ -494,10 +493,158 @@
           <t>PDET</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Transversal del servicio Casas, no de un eje. Aparece en Casas servicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Actividades Sexuales Pagadas</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.2.7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Infancia y Adolescencia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.2.8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Afrocolombiana</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.3.9</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mujer y Equidad</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6.1.9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Seguridad paz y convivencia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.1.7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGBTI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.2.11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LGBTI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.2.12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Comité Intersectorial de Salud</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Centros de escucha</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oculta solo de la card sin código (producto puntual; no afecta cards con código SIRBE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>conducta suicida</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Plan sin código SIRBE en este eje (sus códigos son de Bienestar/Inclusión). No mostrar en sin código.</t>
         </is>
       </c>
     </row>
